--- a/data/trans_orig/P1433-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2012</t>
+          <t>Población con diagnóstico de esterilidad en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>294738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>579910</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581983</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,62 +1109,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6530</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>6391</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499943</t>
+          <t>499900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>520566</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>522656</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1021793</t>
+          <t>1021654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,62 +1452,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1094</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6236</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317878</t>
+          <t>318645</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341020</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>658830</t>
+          <t>659567</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379377</t>
+          <t>380321</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387993</t>
+          <t>387981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>754141</t>
+          <t>754270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761965</t>
+          <t>761982</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -2103,97 +2103,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>212618</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>217613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>430180</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>432209</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2446,97 +2446,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273981</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>276112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278096</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>550077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8647</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>658274</t>
+          <t>658328</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>685206</t>
+          <t>683447</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692815</t>
+          <t>692805</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1346529</t>
+          <t>1346857</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1355567</t>
+          <t>1355558</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>9159</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10491</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>774384</t>
+          <t>774415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812915</t>
+          <t>812455</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820578</t>
+          <t>820571</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1590222</t>
+          <t>1590210</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1599652</t>
+          <t>1599646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>10397</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18645</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3417071</t>
+          <t>3416382</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3424980</t>
+          <t>3424960</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3534381</t>
+          <t>3534272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3547939</t>
+          <t>3547779</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6956174</t>
+          <t>6955798</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6971552</t>
+          <t>6971068</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -3859,7 +3859,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de esterilidad en 2016</t>
+          <t>Población con diagnóstico de esterilidad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4054,97 +4054,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5134</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1020</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5154</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5143</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5039</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291649</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293761</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283549</t>
+          <t>283569</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577425</t>
+          <t>577321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4397,97 +4397,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500548</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>502575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>521013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>523084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1023607</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1025659</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4740,97 +4740,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1882</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>652992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>654874</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5083,97 +5083,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367963</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>369964</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>385212</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387283</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>755208</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>757247</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5426,97 +5426,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1903</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218587</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>427915</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5769,97 +5769,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1969</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263123</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273115</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>534269</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>536238</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648823</t>
+          <t>648863</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655671</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>686051</t>
+          <t>685892</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1337934</t>
+          <t>1338406</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346836</t>
+          <t>1346838</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6455,97 +6455,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2046</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6568,12 +6568,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>776592</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778583</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>824069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>826167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1602704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1604750</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>890</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1828</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3386642</t>
+          <t>3386278</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3393459</t>
+          <t>3393460</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3538135</t>
+          <t>3537421</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6927755</t>
+          <t>6927469</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6937064</t>
+          <t>6937054</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">

--- a/data/trans_orig/P1433-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1433-Provincia-trans_orig.xlsx
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>499900</t>
+          <t>499817</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1021654</t>
+          <t>1021810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>318645</t>
+          <t>317837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>659567</t>
+          <t>659582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>380321</t>
+          <t>380089</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>387981</t>
+          <t>387979</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>754270</t>
+          <t>751851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761982</t>
+          <t>761953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4460</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10406</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>658328</t>
+          <t>658481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>683447</t>
+          <t>684159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692805</t>
+          <t>692809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1346857</t>
+          <t>1346596</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1355558</t>
+          <t>1355588</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4683</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>10556</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>774415</t>
+          <t>774393</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>812455</t>
+          <t>811664</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>820571</t>
+          <t>820565</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1590210</t>
+          <t>1590157</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1599646</t>
+          <t>1599649</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18089</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24007</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3416382</t>
+          <t>3414510</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3424960</t>
+          <t>3424937</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3534272</t>
+          <t>3534937</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3547779</t>
+          <t>3548062</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6955798</t>
+          <t>6956370</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6971068</t>
+          <t>6970732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283569</t>
+          <t>283672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577321</t>
+          <t>577180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>648863</t>
+          <t>648543</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655675</t>
+          <t>655660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>685892</t>
+          <t>686746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1338406</t>
+          <t>1338375</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346838</t>
+          <t>1346829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>888</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6868,12 +6868,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -6911,12 +6911,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3386278</t>
+          <t>3386768</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3393460</t>
+          <t>3393462</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3537421</t>
+          <t>3537416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6927469</t>
+          <t>6928632</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6937054</t>
+          <t>6937069</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
